--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -1391,7 +1391,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
         <v>10</v>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="81">
   <si>
     <t>#</t>
   </si>
@@ -95,7 +95,7 @@
     <t>治愈之甲</t>
   </si>
   <si>
-    <t>财富之袍</t>
+    <t>财富扳指</t>
   </si>
   <si>
     <t>1E+7</t>
@@ -107,16 +107,16 @@
     <t>金币加成增加20%</t>
   </si>
   <si>
-    <t>财富之链</t>
+    <t>财富项链</t>
   </si>
   <si>
     <t>杀敌金币，杀敌金币，杀敌金币，</t>
   </si>
   <si>
-    <t>财富之带</t>
-  </si>
-  <si>
-    <t>修炼之袍</t>
+    <t>财富玉带</t>
+  </si>
+  <si>
+    <t>杀戮血剑</t>
   </si>
   <si>
     <t>1E+8</t>
@@ -128,22 +128,22 @@
     <t>经验加成增加20%</t>
   </si>
   <si>
-    <t>修炼之面</t>
-  </si>
-  <si>
-    <t>修炼之靴</t>
-  </si>
-  <si>
-    <t>神速之链</t>
+    <t>杀戮面罩</t>
+  </si>
+  <si>
+    <t>杀戮战靴</t>
+  </si>
+  <si>
+    <t>狂风之刃</t>
   </si>
   <si>
     <t>攻速增加10%，冷却增加10%</t>
   </si>
   <si>
-    <t>神速之带</t>
-  </si>
-  <si>
-    <t>神速之靴</t>
+    <t>狂风项链</t>
+  </si>
+  <si>
+    <t>狂风戒指</t>
   </si>
   <si>
     <t>重击之刃</t>
@@ -1257,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -1644,14 +1644,10 @@
       <c r="J15" s="8"/>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
       <c r="C16" s="3">
-        <v>211010</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>35</v>
@@ -1670,14 +1666,10 @@
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
       <c r="C17" s="3">
-        <v>211011</v>
+        <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>37</v>
@@ -1692,14 +1684,10 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
       <c r="C18" s="3">
-        <v>211012</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>38</v>
@@ -1713,31 +1701,17 @@
       <c r="I18" s="2"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>211013</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>39</v>
-      </c>
+    <row r="19" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3">
-        <v>4</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>40</v>
-      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A20" s="3" t="s">
@@ -1747,19 +1721,23 @@
         <v>0</v>
       </c>
       <c r="C20" s="3">
-        <v>211014</v>
+        <v>211013</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
         <v>4</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A21" s="3" t="s">
@@ -1769,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="3">
-        <v>211015</v>
+        <v>211014</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1791,23 +1769,19 @@
         <v>0</v>
       </c>
       <c r="C22" s="3">
-        <v>211016</v>
+        <v>211015</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>7</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>45</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A23" s="3" t="s">
@@ -1817,19 +1791,23 @@
         <v>0</v>
       </c>
       <c r="C23" s="3">
-        <v>211017</v>
+        <v>211016</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3">
         <v>7</v>
       </c>
-      <c r="H23" s="2"/>
+      <c r="H23" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A24" s="3" t="s">
@@ -1839,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="3">
-        <v>211018</v>
+        <v>211017</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1854,40 +1832,38 @@
       <c r="J24" s="3"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3">
+        <v>211018</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
+      <c r="G25" s="3">
+        <v>7</v>
+      </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3">
-        <v>211004</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3">
-        <v>2</v>
-      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A27" s="3" t="s">
@@ -1897,10 +1873,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="3">
-        <v>211005</v>
+        <v>211004</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1909,7 +1885,9 @@
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A28" s="3" t="s">
@@ -1919,10 +1897,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="3">
-        <v>211006</v>
+        <v>211005</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1933,29 +1911,27 @@
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3">
-        <v>211019</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3">
-        <v>8</v>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="3" t="s">
-        <v>54</v>
-      </c>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3">
+        <v>211006</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3">
+        <v>2</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="3" t="s">
@@ -1965,10 +1941,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="3">
-        <v>211020</v>
+        <v>211019</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1977,7 +1953,9 @@
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="3" t="s">
@@ -1987,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <v>211021</v>
+        <v>211020</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2009,21 +1987,19 @@
         <v>0</v>
       </c>
       <c r="C34" s="3">
-        <v>211022</v>
+        <v>211021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A35" s="3" t="s">
@@ -2033,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="3">
-        <v>211023</v>
+        <v>211022</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2045,7 +2021,9 @@
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A36" s="3" t="s">
@@ -2055,10 +2033,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3">
-        <v>211024</v>
+        <v>211023</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2077,21 +2055,19 @@
         <v>0</v>
       </c>
       <c r="C37" s="3">
-        <v>211025</v>
+        <v>211024</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A38" s="3" t="s">
@@ -2101,10 +2077,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="3">
-        <v>211026</v>
+        <v>211025</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2113,7 +2089,9 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="3"/>
+      <c r="J38" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A39" s="3" t="s">
@@ -2123,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="3">
-        <v>211027</v>
+        <v>211026</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2137,51 +2115,51 @@
       <c r="I39" s="2"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="3">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3">
+        <v>211027</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3">
+        <v>6</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A43" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3">
         <v>211031</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8">
-        <v>13</v>
-      </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A43" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="3">
-        <v>211032</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
       <c r="G43" s="8">
         <v>13</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="3"/>
+      <c r="J43" s="8" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A44" s="3" t="s">
@@ -2191,10 +2169,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="3">
-        <v>211033</v>
+        <v>211032</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2213,21 +2191,19 @@
         <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>211034</v>
+        <v>211033</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="3">
-        <v>14</v>
+      <c r="G45" s="8">
+        <v>13</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A46" s="3" t="s">
@@ -2237,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="3">
-        <v>211035</v>
+        <v>211034</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2249,7 +2225,9 @@
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="3"/>
+      <c r="J46" s="3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A47" s="3" t="s">
@@ -2259,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="3">
-        <v>211036</v>
+        <v>211035</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2281,21 +2259,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3">
-        <v>211037</v>
+        <v>211036</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A49" s="3" t="s">
@@ -2305,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>211038</v>
+        <v>211037</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2317,7 +2293,9 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="3"/>
+      <c r="J49" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A50" s="3" t="s">
@@ -2327,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="3">
-        <v>211039</v>
+        <v>211038</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2349,21 +2327,19 @@
         <v>0</v>
       </c>
       <c r="C51" s="3">
-        <v>211040</v>
+        <v>211039</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="3" t="s">
-        <v>78</v>
-      </c>
+      <c r="J51" s="3"/>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A52" s="3" t="s">
@@ -2373,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="3">
-        <v>211041</v>
+        <v>211040</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2385,7 +2361,9 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="3"/>
+      <c r="J52" s="3" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A53" s="3" t="s">
@@ -2395,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="3">
-        <v>211042</v>
+        <v>211041</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2408,6 +2386,28 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A54" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3">
+        <v>211042</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3">
+        <v>3</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -134,7 +134,13 @@
     <t>杀戮战靴</t>
   </si>
   <si>
-    <t>狂风之刃</t>
+    <t>狂风影刃</t>
+  </si>
+  <si>
+    <t>5E+8</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>攻速增加10%，冷却增加10%</t>
@@ -1652,17 +1658,23 @@
       <c r="D16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="3">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3">
+        <v>10</v>
+      </c>
       <c r="G16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="J16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:10">
@@ -1672,15 +1684,23 @@
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="3">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3">
-        <v>5</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
       <c r="J17" s="3"/>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:10">
@@ -1690,15 +1710,23 @@
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="E18" s="3">
+        <v>11</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5</v>
+      </c>
       <c r="G18" s="3">
-        <v>5</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="J18" s="3"/>
     </row>
     <row r="19" customFormat="1" customHeight="1" spans="1:10">
@@ -1724,7 +1752,7 @@
         <v>211013</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1732,11 +1760,11 @@
         <v>4</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1750,7 +1778,7 @@
         <v>211014</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1772,7 +1800,7 @@
         <v>211015</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1794,7 +1822,7 @@
         <v>211016</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -1802,11 +1830,11 @@
         <v>7</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1820,7 +1848,7 @@
         <v>211017</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1842,7 +1870,7 @@
         <v>211018</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1876,7 +1904,7 @@
         <v>211004</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1886,7 +1914,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1900,7 +1928,7 @@
         <v>211005</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1922,7 +1950,7 @@
         <v>211006</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1944,7 +1972,7 @@
         <v>211019</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1954,7 +1982,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1968,7 +1996,7 @@
         <v>211020</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -1990,7 +2018,7 @@
         <v>211021</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2012,7 +2040,7 @@
         <v>211022</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2022,7 +2050,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2036,7 +2064,7 @@
         <v>211023</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2058,7 +2086,7 @@
         <v>211024</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2080,7 +2108,7 @@
         <v>211025</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2090,7 +2118,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2104,7 +2132,7 @@
         <v>211026</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2126,7 +2154,7 @@
         <v>211027</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2148,7 +2176,7 @@
         <v>211031</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
@@ -2158,7 +2186,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2172,7 +2200,7 @@
         <v>211032</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2194,7 +2222,7 @@
         <v>211033</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2216,7 +2244,7 @@
         <v>211034</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2226,7 +2254,7 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2240,7 +2268,7 @@
         <v>211035</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2262,7 +2290,7 @@
         <v>211036</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2284,7 +2312,7 @@
         <v>211037</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2294,7 +2322,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2308,7 +2336,7 @@
         <v>211038</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2330,7 +2358,7 @@
         <v>211039</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2352,7 +2380,7 @@
         <v>211040</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2362,7 +2390,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
       <c r="J52" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2376,7 +2404,7 @@
         <v>211041</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2398,7 +2426,7 @@
         <v>211042</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -98,7 +98,7 @@
     <t>财富扳指</t>
   </si>
   <si>
-    <t>1E+7</t>
+    <t>2E+6</t>
   </si>
   <si>
     <t>8</t>
@@ -119,7 +119,7 @@
     <t>杀戮血剑</t>
   </si>
   <si>
-    <t>1E+8</t>
+    <t>3E+6</t>
   </si>
   <si>
     <t>15</t>
@@ -137,7 +137,7 @@
     <t>狂风影刃</t>
   </si>
   <si>
-    <t>5E+8</t>
+    <t>4E+6</t>
   </si>
   <si>
     <t>30</t>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -134,7 +134,7 @@
     <t>杀戮战靴</t>
   </si>
   <si>
-    <t>狂风影刃</t>
+    <t>狂风面具</t>
   </si>
   <si>
     <t>4E+6</t>
@@ -149,37 +149,46 @@
     <t>狂风项链</t>
   </si>
   <si>
+    <t>cd，攻速，命中</t>
+  </si>
+  <si>
     <t>狂风戒指</t>
   </si>
   <si>
-    <t>重击之刃</t>
-  </si>
-  <si>
-    <t>2E+8</t>
+    <t>重击巨剑</t>
+  </si>
+  <si>
+    <t>5E+6</t>
   </si>
   <si>
     <t>此次攻击概率翻倍</t>
   </si>
   <si>
-    <t>重击之链</t>
-  </si>
-  <si>
-    <t>重击之戒</t>
-  </si>
-  <si>
-    <t>暴击之剑</t>
-  </si>
-  <si>
-    <t>3E+8</t>
+    <t>重击护腕</t>
+  </si>
+  <si>
+    <t>攻击加成，攻击加成，攻击加成</t>
+  </si>
+  <si>
+    <t>重击腰带</t>
+  </si>
+  <si>
+    <t>暴击扳指</t>
+  </si>
+  <si>
+    <t>7E+6</t>
   </si>
   <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
   </si>
   <si>
-    <t>暴击之链</t>
-  </si>
-  <si>
-    <t>暴击之戒</t>
+    <t>暴击板甲</t>
+  </si>
+  <si>
+    <t>暴击，爆伤，增伤</t>
+  </si>
+  <si>
+    <t>暴击铁履</t>
   </si>
   <si>
     <t>天命之剑</t>
@@ -1263,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -1701,7 +1710,9 @@
       <c r="I17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:10">
       <c r="A18" s="3"/>
@@ -1710,7 +1721,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" s="3">
         <v>11</v>
@@ -1729,169 +1740,205 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" customFormat="1" customHeight="1" spans="1:10">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
+      <c r="C19" s="3">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F19" s="3">
+        <v>10</v>
+      </c>
+      <c r="G19" s="3">
+        <v>5</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="2">
+        <v>40</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
       <c r="C20" s="3">
-        <v>211013</v>
+        <v>14</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F20" s="3">
+        <v>10</v>
+      </c>
       <c r="G20" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="I20" s="2">
+        <v>40</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
       <c r="C21" s="3">
-        <v>211014</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+        <v>47</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F21" s="3">
+        <v>10</v>
+      </c>
       <c r="G21" s="3">
-        <v>4</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="2">
+        <v>40</v>
+      </c>
       <c r="J21" s="3"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A22" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
       <c r="C22" s="3">
-        <v>211015</v>
+        <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="E22" s="3">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5</v>
+      </c>
       <c r="G22" s="3">
-        <v>4</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="2">
+        <v>50</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
       <c r="C23" s="3">
-        <v>211016</v>
+        <v>17</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22</v>
+      </c>
+      <c r="F23" s="3">
+        <v>20</v>
+      </c>
       <c r="G23" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="I23" s="2">
+        <v>50</v>
+      </c>
       <c r="J23" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="3">
-        <v>211017</v>
+        <v>18</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="3">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>6</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3">
-        <v>7</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2">
+        <v>50</v>
+      </c>
       <c r="J24" s="3"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="3">
-        <v>211018</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
-      <c r="G25" s="3">
-        <v>7</v>
-      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3">
+        <v>211004</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
+      <c r="G26" s="3">
+        <v>2</v>
+      </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A27" s="3" t="s">
@@ -1901,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="3">
-        <v>211004</v>
+        <v>211005</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1913,9 +1960,7 @@
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
-      <c r="J27" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="J27" s="3"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A28" s="3" t="s">
@@ -1925,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="3">
-        <v>211005</v>
+        <v>211006</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1939,27 +1984,29 @@
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A29" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3">
-        <v>211006</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3">
-        <v>2</v>
-      </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="3"/>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3">
+        <v>211019</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3">
+        <v>8</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="3" t="s">
@@ -1969,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="3">
-        <v>211019</v>
+        <v>211020</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -1981,9 +2028,7 @@
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
-      <c r="J32" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A33" s="3" t="s">
@@ -1993,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <v>211020</v>
+        <v>211021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2015,19 +2060,21 @@
         <v>0</v>
       </c>
       <c r="C34" s="3">
-        <v>211021</v>
+        <v>211022</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A35" s="3" t="s">
@@ -2037,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="3">
-        <v>211022</v>
+        <v>211023</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2049,9 +2096,7 @@
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
-      <c r="J35" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A36" s="3" t="s">
@@ -2061,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3">
-        <v>211023</v>
+        <v>211024</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2083,19 +2128,21 @@
         <v>0</v>
       </c>
       <c r="C37" s="3">
-        <v>211024</v>
+        <v>211025</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
-      <c r="J37" s="3"/>
+      <c r="J37" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A38" s="3" t="s">
@@ -2105,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="3">
-        <v>211025</v>
+        <v>211026</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2117,9 +2164,7 @@
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A39" s="3" t="s">
@@ -2129,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="3">
-        <v>211026</v>
+        <v>211027</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2143,29 +2188,31 @@
       <c r="I39" s="2"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A40" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3">
-        <v>211027</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3">
-        <v>6</v>
-      </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="1:10">
+    <row r="42" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3">
+        <v>211031</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8">
+        <v>13</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A43" s="3" t="s">
         <v>0</v>
       </c>
@@ -2173,21 +2220,19 @@
         <v>0</v>
       </c>
       <c r="C43" s="3">
-        <v>211031</v>
+        <v>211032</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
       <c r="G43" s="8">
         <v>13</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="8" t="s">
-        <v>68</v>
-      </c>
+      <c r="J43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A44" s="3" t="s">
@@ -2197,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="3">
-        <v>211032</v>
+        <v>211033</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2219,19 +2264,21 @@
         <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>211033</v>
+        <v>211034</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
-      <c r="G45" s="8">
-        <v>13</v>
+      <c r="G45" s="3">
+        <v>14</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A46" s="3" t="s">
@@ -2241,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="3">
-        <v>211034</v>
+        <v>211035</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2253,9 +2300,7 @@
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="3" t="s">
-        <v>72</v>
-      </c>
+      <c r="J46" s="3"/>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A47" s="3" t="s">
@@ -2265,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="3">
-        <v>211035</v>
+        <v>211036</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2287,19 +2332,21 @@
         <v>0</v>
       </c>
       <c r="C48" s="3">
-        <v>211036</v>
+        <v>211037</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A49" s="3" t="s">
@@ -2309,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>211037</v>
+        <v>211038</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2321,9 +2368,7 @@
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="J49" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="J49" s="3"/>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A50" s="3" t="s">
@@ -2333,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="3">
-        <v>211038</v>
+        <v>211039</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2355,19 +2400,21 @@
         <v>0</v>
       </c>
       <c r="C51" s="3">
-        <v>211039</v>
+        <v>211040</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
-      <c r="J51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A52" s="3" t="s">
@@ -2377,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="3">
-        <v>211040</v>
+        <v>211041</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2389,9 +2436,7 @@
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
-      <c r="J52" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A53" s="3" t="s">
@@ -2401,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="3">
-        <v>211041</v>
+        <v>211042</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2414,28 +2459,6 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3">
-        <v>211042</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3">
-        <v>3</v>
-      </c>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -89,7 +89,7 @@
     <t>治愈之镯</t>
   </si>
   <si>
-    <t>减伤，诅咒，闪避</t>
+    <t>减伤，防御，闪避</t>
   </si>
   <si>
     <t>治愈之甲</t>
@@ -1462,10 +1462,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="3">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
+        <v>1002</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
       </c>
       <c r="G8" s="3">
         <v>1</v>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -1491,7 +1491,7 @@
         <v>85</v>
       </c>
       <c r="F9" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" ref="G9:G14" si="0">G6+1</f>
@@ -1520,7 +1520,7 @@
         <v>85</v>
       </c>
       <c r="F10" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
@@ -1549,7 +1549,7 @@
         <v>85</v>
       </c>
       <c r="F11" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
@@ -1576,7 +1576,7 @@
         <v>86</v>
       </c>
       <c r="F12" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
@@ -1605,7 +1605,7 @@
         <v>86</v>
       </c>
       <c r="F13" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
@@ -1632,7 +1632,7 @@
         <v>86</v>
       </c>
       <c r="F14" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="82">
   <si>
     <t>#</t>
   </si>
@@ -80,9 +80,6 @@
     <t>1E+6</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>回复效果提高100%</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>2E+6</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>金币加成增加20%</t>
   </si>
   <si>
@@ -119,10 +113,7 @@
     <t>杀戮血剑</t>
   </si>
   <si>
-    <t>3E+6</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>4E+6</t>
   </si>
   <si>
     <t>经验加成增加20%</t>
@@ -137,10 +128,7 @@
     <t>狂风面具</t>
   </si>
   <si>
-    <t>4E+6</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>7E+6</t>
   </si>
   <si>
     <t>攻速增加10%，冷却增加10%</t>
@@ -158,7 +146,7 @@
     <t>重击巨剑</t>
   </si>
   <si>
-    <t>5E+6</t>
+    <t>1E+7</t>
   </si>
   <si>
     <t>此次攻击概率翻倍</t>
@@ -176,7 +164,7 @@
     <t>暴击扳指</t>
   </si>
   <si>
-    <t>7E+6</t>
+    <t>2E+7</t>
   </si>
   <si>
     <t>如果此次攻击暴击了，伤害额外翻倍</t>
@@ -1417,11 +1405,11 @@
       <c r="H6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1431,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="3">
         <v>14</v>
@@ -1445,11 +1433,11 @@
       <c r="H7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="9" t="s">
-        <v>17</v>
+      <c r="I7" s="2">
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1459,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3">
         <v>1002</v>
@@ -1473,8 +1461,8 @@
       <c r="H8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>17</v>
+      <c r="I8" s="2">
+        <v>3</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -1485,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3">
         <v>85</v>
@@ -1498,13 +1486,13 @@
         <v>2</v>
       </c>
       <c r="H9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1514,7 +1502,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3">
         <v>85</v>
@@ -1527,13 +1515,13 @@
         <v>2</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1543,7 +1531,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
         <v>85</v>
@@ -1556,10 +1544,10 @@
         <v>2</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -1570,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>86</v>
@@ -1583,13 +1571,13 @@
         <v>3</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="I12" s="2">
+        <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:10">
@@ -1599,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
         <v>86</v>
@@ -1612,10 +1600,10 @@
         <v>3</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="I13" s="2">
+        <v>15</v>
       </c>
       <c r="J13" s="8"/>
     </row>
@@ -1626,7 +1614,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3">
         <v>86</v>
@@ -1639,10 +1627,10 @@
         <v>3</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="I14" s="2">
+        <v>15</v>
       </c>
       <c r="J14" s="8"/>
     </row>
@@ -1665,7 +1653,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E16" s="3">
         <v>13</v>
@@ -1677,13 +1665,13 @@
         <v>4</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="I16" s="2">
+        <v>30</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:10">
@@ -1693,7 +1681,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E17" s="3">
         <v>10</v>
@@ -1705,13 +1693,13 @@
         <v>4</v>
       </c>
       <c r="H17" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="2">
+        <v>30</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="1" customHeight="1" spans="1:10">
@@ -1721,7 +1709,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E18" s="3">
         <v>11</v>
@@ -1733,10 +1721,10 @@
         <v>4</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="I18" s="2">
+        <v>30</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -1747,7 +1735,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E19" s="3">
         <v>1003</v>
@@ -1759,13 +1747,13 @@
         <v>5</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I19" s="2">
+        <v>50</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1775,7 +1763,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E20" s="3">
         <v>1003</v>
@@ -1787,13 +1775,13 @@
         <v>5</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I20" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1803,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E21" s="3">
         <v>1003</v>
@@ -1815,10 +1803,10 @@
         <v>5</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I21" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J21" s="3"/>
     </row>
@@ -1829,7 +1817,7 @@
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3">
         <v>21</v>
@@ -1841,13 +1829,13 @@
         <v>6</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I22" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1857,7 +1845,7 @@
         <v>17</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E23" s="3">
         <v>22</v>
@@ -1869,13 +1857,13 @@
         <v>6</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I23" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1885,7 +1873,7 @@
         <v>18</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3">
         <v>27</v>
@@ -1897,10 +1885,10 @@
         <v>6</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I24" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J24" s="3"/>
     </row>
@@ -1927,7 +1915,7 @@
         <v>211004</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1937,7 +1925,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1951,7 +1939,7 @@
         <v>211005</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1973,7 +1961,7 @@
         <v>211006</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -1995,7 +1983,7 @@
         <v>211019</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2005,7 +1993,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2019,7 +2007,7 @@
         <v>211020</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2041,7 +2029,7 @@
         <v>211021</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2063,7 +2051,7 @@
         <v>211022</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2073,7 +2061,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2087,7 +2075,7 @@
         <v>211023</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2109,7 +2097,7 @@
         <v>211024</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2131,7 +2119,7 @@
         <v>211025</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2141,7 +2129,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2155,7 +2143,7 @@
         <v>211026</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2177,7 +2165,7 @@
         <v>211027</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2199,7 +2187,7 @@
         <v>211031</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -2209,7 +2197,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2223,7 +2211,7 @@
         <v>211032</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2245,7 +2233,7 @@
         <v>211033</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2267,7 +2255,7 @@
         <v>211034</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2277,7 +2265,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2291,7 +2279,7 @@
         <v>211035</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2313,7 +2301,7 @@
         <v>211036</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2335,7 +2323,7 @@
         <v>211037</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2345,7 +2333,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2359,7 +2347,7 @@
         <v>211038</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2381,7 +2369,7 @@
         <v>211039</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2403,7 +2391,7 @@
         <v>211040</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2413,7 +2401,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2427,7 +2415,7 @@
         <v>211041</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2449,7 +2437,7 @@
         <v>211042</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -179,9 +184,27 @@
     <t>暴击铁履</t>
   </si>
   <si>
+    <t>致命之剑</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
+  </si>
+  <si>
+    <t>致命之镯</t>
+  </si>
+  <si>
+    <t>致命之戒</t>
+  </si>
+  <si>
     <t>天命之剑</t>
   </si>
   <si>
+    <t>5E+8</t>
+  </si>
+  <si>
     <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
   </si>
   <si>
@@ -189,18 +212,6 @@
   </si>
   <si>
     <t>天命之戒</t>
-  </si>
-  <si>
-    <t>致命之剑</t>
-  </si>
-  <si>
-    <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
-  </si>
-  <si>
-    <t>致命之镯</t>
-  </si>
-  <si>
-    <t>致命之戒</t>
   </si>
   <si>
     <t>背刺之匕</t>
@@ -1260,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -1637,29 +1648,45 @@
     <row r="15" customFormat="1" customHeight="1" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="8"/>
+      <c r="C15" s="3">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="2">
+        <v>30</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:10">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="3">
-        <v>13</v>
-      </c>
       <c r="F16" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="3">
         <v>4</v>
@@ -1671,20 +1698,20 @@
         <v>30</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="1" customHeight="1" spans="1:10">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3">
+        <v>12</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="3">
         <v>11</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="3">
-        <v>10</v>
       </c>
       <c r="F17" s="3">
         <v>5</v>
@@ -1698,44 +1725,44 @@
       <c r="I17" s="2">
         <v>30</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E18" s="3">
-        <v>11</v>
+        <v>1003</v>
       </c>
       <c r="F18" s="3">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3">
         <v>5</v>
       </c>
-      <c r="G18" s="3">
-        <v>4</v>
-      </c>
       <c r="H18" s="9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I18" s="2">
-        <v>30</v>
-      </c>
-      <c r="J18" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E19" s="3">
         <v>1003</v>
@@ -1752,18 +1779,18 @@
       <c r="I19" s="2">
         <v>50</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>40</v>
+      <c r="J19" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" s="3">
         <v>1003</v>
@@ -1780,50 +1807,50 @@
       <c r="I20" s="2">
         <v>50</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="3">
-        <v>1003</v>
+        <v>21</v>
       </c>
       <c r="F21" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I21" s="2">
-        <v>50</v>
-      </c>
-      <c r="J21" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3">
         <v>6</v>
@@ -1835,23 +1862,22 @@
         <v>80</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
       <c r="C23" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G23" s="3">
         <v>6</v>
@@ -1862,116 +1888,178 @@
       <c r="I23" s="2">
         <v>80</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
       <c r="C24" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3">
         <v>5</v>
       </c>
       <c r="G24" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="2">
-        <v>80</v>
-      </c>
-      <c r="J24" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="2"/>
+      <c r="C25" s="3">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="3">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3">
+        <v>30</v>
+      </c>
+      <c r="G25" s="3">
+        <v>7</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="3">
-        <v>211004</v>
+        <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>10</v>
+      </c>
       <c r="G26" s="3">
-        <v>2</v>
-      </c>
-      <c r="H26" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="I26" s="2"/>
-      <c r="J26" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="J26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A27" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
       <c r="C27" s="3">
-        <v>211005</v>
+        <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2003</v>
+      </c>
+      <c r="F27" s="3">
+        <v>20</v>
+      </c>
       <c r="G27" s="3">
-        <v>2</v>
-      </c>
-      <c r="H27" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="I27" s="2"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A28" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="3">
-        <v>211006</v>
+        <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E28" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" s="3">
+        <v>15</v>
+      </c>
       <c r="G28" s="3">
-        <v>2</v>
-      </c>
-      <c r="H28" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>56</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="3"/>
     </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3">
+        <v>24</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="3">
+        <v>13</v>
+      </c>
+      <c r="F29" s="3">
+        <v>15</v>
+      </c>
+      <c r="G29" s="3">
+        <v>8</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3">
+        <v>211022</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3">
+        <v>9</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A31" s="3" t="s">
         <v>0</v>
@@ -1980,21 +2068,19 @@
         <v>0</v>
       </c>
       <c r="C31" s="3">
-        <v>211019</v>
+        <v>211023</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
-      <c r="J31" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="J31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A32" s="3" t="s">
@@ -2004,15 +2090,15 @@
         <v>0</v>
       </c>
       <c r="C32" s="3">
-        <v>211020</v>
+        <v>211024</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2026,19 +2112,21 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <v>211021</v>
+        <v>211025</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A34" s="3" t="s">
@@ -2048,21 +2136,19 @@
         <v>0</v>
       </c>
       <c r="C34" s="3">
-        <v>211022</v>
+        <v>211026</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
-      <c r="J34" s="3" t="s">
-        <v>59</v>
-      </c>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A35" s="3" t="s">
@@ -2072,67 +2158,21 @@
         <v>0</v>
       </c>
       <c r="C35" s="3">
-        <v>211023</v>
+        <v>211027</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A36" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="3">
-        <v>211024</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3">
-        <v>9</v>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A37" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" s="3">
-        <v>211025</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3">
-        <v>6</v>
-      </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="38" customFormat="1" customHeight="1" spans="1:10">
       <c r="A38" s="3" t="s">
         <v>0</v>
       </c>
@@ -2140,19 +2180,21 @@
         <v>0</v>
       </c>
       <c r="C38" s="3">
-        <v>211026</v>
+        <v>211031</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8">
+        <v>13</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="3"/>
+      <c r="J38" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A39" s="3" t="s">
@@ -2162,21 +2204,67 @@
         <v>0</v>
       </c>
       <c r="C39" s="3">
-        <v>211027</v>
+        <v>211032</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-      <c r="G39" s="3">
-        <v>6</v>
+      <c r="G39" s="8">
+        <v>13</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="3"/>
     </row>
-    <row r="42" customFormat="1" customHeight="1" spans="1:10">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3">
+        <v>211033</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="8">
+        <v>13</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3">
+        <v>211034</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3">
+        <v>14</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
@@ -2184,21 +2272,19 @@
         <v>0</v>
       </c>
       <c r="C42" s="3">
-        <v>211031</v>
+        <v>211035</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8">
-        <v>13</v>
+        <v>74</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3">
+        <v>14</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="8" t="s">
-        <v>67</v>
-      </c>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A43" s="3" t="s">
@@ -2208,15 +2294,15 @@
         <v>0</v>
       </c>
       <c r="C43" s="3">
-        <v>211032</v>
+        <v>211036</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="8">
-        <v>13</v>
+      <c r="G43" s="3">
+        <v>14</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2230,19 +2316,21 @@
         <v>0</v>
       </c>
       <c r="C44" s="3">
-        <v>211033</v>
+        <v>211037</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="8">
-        <v>13</v>
+      <c r="G44" s="3">
+        <v>10</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="3"/>
+      <c r="J44" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A45" s="3" t="s">
@@ -2252,21 +2340,19 @@
         <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>211034</v>
+        <v>211038</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="J45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A46" s="3" t="s">
@@ -2276,15 +2362,15 @@
         <v>0</v>
       </c>
       <c r="C46" s="3">
-        <v>211035</v>
+        <v>211039</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2298,19 +2384,21 @@
         <v>0</v>
       </c>
       <c r="C47" s="3">
-        <v>211036</v>
+        <v>211040</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="3"/>
+      <c r="J47" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A48" s="3" t="s">
@@ -2320,21 +2408,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3">
-        <v>211037</v>
+        <v>211041</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A49" s="3" t="s">
@@ -2344,109 +2430,19 @@
         <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>211038</v>
+        <v>211042</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C50" s="3">
-        <v>211039</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3">
-        <v>10</v>
-      </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A51" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="3">
-        <v>211040</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3">
-        <v>3</v>
-      </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A52" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="3">
-        <v>211041</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3">
-        <v>3</v>
-      </c>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C53" s="3">
-        <v>211042</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3">
-        <v>3</v>
-      </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -187,7 +187,7 @@
     <t>致命之剑</t>
   </si>
   <si>
-    <t>1E+8</t>
+    <t>4E+7</t>
   </si>
   <si>
     <t>如果此次触发了致命攻击了，伤害额外翻倍</t>
@@ -202,7 +202,7 @@
     <t>天命之剑</t>
   </si>
   <si>
-    <t>5E+8</t>
+    <t>5E+7</t>
   </si>
   <si>
     <t>攻击概率降低50%，概率2倍，5倍，10倍，100倍</t>
@@ -214,28 +214,34 @@
     <t>天命之戒</t>
   </si>
   <si>
-    <t>背刺之匕</t>
+    <t>福运护面</t>
+  </si>
+  <si>
+    <t>6E+7</t>
   </si>
   <si>
     <t>首次攻击敌人，降低敌人10%最大生命</t>
   </si>
   <si>
-    <t>背刺之带</t>
-  </si>
-  <si>
-    <t>背刺之靴</t>
-  </si>
-  <si>
-    <t>坚韧之甲</t>
+    <t>福运护手</t>
+  </si>
+  <si>
+    <t>福运护袍</t>
+  </si>
+  <si>
+    <t>寻宝扳指</t>
+  </si>
+  <si>
+    <t>7E+7</t>
   </si>
   <si>
     <t>最高承伤10%</t>
   </si>
   <si>
-    <t>坚韧之盔</t>
-  </si>
-  <si>
-    <t>坚韧之带</t>
+    <t>寻宝项链</t>
+  </si>
+  <si>
+    <t>寻宝玉带</t>
   </si>
   <si>
     <t>幸运项链</t>
@@ -1271,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -1585,7 +1591,7 @@
         <v>28</v>
       </c>
       <c r="I12" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>29</v>
@@ -1614,7 +1620,7 @@
         <v>28</v>
       </c>
       <c r="I13" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J13" s="8"/>
     </row>
@@ -1641,7 +1647,7 @@
         <v>28</v>
       </c>
       <c r="I14" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J14" s="8"/>
     </row>
@@ -1667,7 +1673,7 @@
         <v>33</v>
       </c>
       <c r="I15" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>34</v>
@@ -1695,7 +1701,7 @@
         <v>33</v>
       </c>
       <c r="I16" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>36</v>
@@ -1723,7 +1729,7 @@
         <v>33</v>
       </c>
       <c r="I17" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -1749,7 +1755,7 @@
         <v>39</v>
       </c>
       <c r="I18" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>40</v>
@@ -1777,7 +1783,7 @@
         <v>39</v>
       </c>
       <c r="I19" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>42</v>
@@ -1805,7 +1811,7 @@
         <v>39</v>
       </c>
       <c r="I20" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -1831,7 +1837,7 @@
         <v>45</v>
       </c>
       <c r="I21" s="2">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>46</v>
@@ -1859,7 +1865,7 @@
         <v>45</v>
       </c>
       <c r="I22" s="2">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>48</v>
@@ -1886,7 +1892,7 @@
         <v>45</v>
       </c>
       <c r="I23" s="2">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="J23" s="3"/>
     </row>
@@ -1910,7 +1916,9 @@
       <c r="H24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2">
+        <v>30</v>
+      </c>
       <c r="J24" s="3" t="s">
         <v>52</v>
       </c>
@@ -1935,7 +1943,9 @@
       <c r="H25" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2">
+        <v>30</v>
+      </c>
       <c r="J25" s="3"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1959,7 +1969,9 @@
       <c r="H26" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2">
+        <v>30</v>
+      </c>
       <c r="J26" s="3"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1983,7 +1995,9 @@
       <c r="H27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="2">
+        <v>35</v>
+      </c>
       <c r="J27" s="3" t="s">
         <v>57</v>
       </c>
@@ -2009,7 +2023,9 @@
       <c r="H28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I28" s="2"/>
+      <c r="I28" s="2">
+        <v>35</v>
+      </c>
       <c r="J28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2033,238 +2049,220 @@
       <c r="H29" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="2"/>
+      <c r="I29" s="2">
+        <v>35</v>
+      </c>
       <c r="J29" s="3"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="3">
-        <v>211022</v>
+        <v>25</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
+      <c r="E30" s="3">
+        <v>81</v>
+      </c>
+      <c r="F30" s="3">
+        <v>10</v>
+      </c>
       <c r="G30" s="3">
         <v>9</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
+      <c r="H30" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="2">
+        <v>40</v>
+      </c>
       <c r="J30" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
       <c r="C31" s="3">
-        <v>211023</v>
+        <v>26</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="E31" s="3">
+        <v>83</v>
+      </c>
+      <c r="F31" s="3">
+        <v>5</v>
+      </c>
       <c r="G31" s="3">
         <v>9</v>
       </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
+      <c r="H31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="2">
+        <v>40</v>
+      </c>
       <c r="J31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A32" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
       <c r="C32" s="3">
-        <v>211024</v>
+        <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="E32" s="3">
+        <v>82</v>
+      </c>
+      <c r="F32" s="3">
+        <v>10</v>
+      </c>
       <c r="G32" s="3">
         <v>9</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
+      <c r="H32" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I32" s="2">
+        <v>40</v>
+      </c>
       <c r="J32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A33" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
       <c r="C33" s="3">
-        <v>211025</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="E33" s="3">
+        <v>84</v>
+      </c>
+      <c r="F33" s="3">
+        <v>5</v>
+      </c>
       <c r="G33" s="3">
-        <v>6</v>
-      </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I33" s="2">
+        <v>45</v>
+      </c>
       <c r="J33" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
       <c r="C34" s="3">
-        <v>211026</v>
+        <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="3">
+        <v>81</v>
+      </c>
+      <c r="F34" s="3">
+        <v>10</v>
+      </c>
+      <c r="G34" s="3">
+        <v>10</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3">
-        <v>6</v>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
+      <c r="I34" s="2">
+        <v>45</v>
+      </c>
       <c r="J34" s="3"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A35" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>0</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
       <c r="C35" s="3">
-        <v>211027</v>
+        <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="E35" s="3">
+        <v>82</v>
+      </c>
+      <c r="F35" s="3">
+        <v>10</v>
+      </c>
       <c r="G35" s="3">
-        <v>6</v>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="2">
+        <v>45</v>
+      </c>
       <c r="J35" s="3"/>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A38" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="3">
-        <v>211031</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8">
-        <v>13</v>
-      </c>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
-      <c r="J38" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="3">
-        <v>211032</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="8">
-        <v>13</v>
-      </c>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
-      <c r="J39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A40" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3">
-        <v>211033</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="8">
-        <v>13</v>
-      </c>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A41" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="3">
-        <v>211034</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3">
-        <v>14</v>
-      </c>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
-      <c r="J41" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:10">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
@@ -2272,19 +2270,21 @@
         <v>0</v>
       </c>
       <c r="C42" s="3">
-        <v>211035</v>
+        <v>211031</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3">
-        <v>14</v>
+        <v>70</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8">
+        <v>13</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="3"/>
+      <c r="J42" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A43" s="3" t="s">
@@ -2294,15 +2294,15 @@
         <v>0</v>
       </c>
       <c r="C43" s="3">
-        <v>211036</v>
+        <v>211032</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-      <c r="G43" s="3">
-        <v>14</v>
+      <c r="G43" s="8">
+        <v>13</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2316,21 +2316,19 @@
         <v>0</v>
       </c>
       <c r="C44" s="3">
-        <v>211037</v>
+        <v>211033</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="3">
-        <v>10</v>
+      <c r="G44" s="8">
+        <v>13</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
-      <c r="J44" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A45" s="3" t="s">
@@ -2340,19 +2338,21 @@
         <v>0</v>
       </c>
       <c r="C45" s="3">
-        <v>211038</v>
+        <v>211034</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="3"/>
+      <c r="J45" s="3" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A46" s="3" t="s">
@@ -2362,15 +2362,15 @@
         <v>0</v>
       </c>
       <c r="C46" s="3">
-        <v>211039</v>
+        <v>211035</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2384,21 +2384,19 @@
         <v>0</v>
       </c>
       <c r="C47" s="3">
-        <v>211040</v>
+        <v>211036</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="J47" s="3"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A48" s="3" t="s">
@@ -2408,19 +2406,21 @@
         <v>0</v>
       </c>
       <c r="C48" s="3">
-        <v>211041</v>
+        <v>211037</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-      <c r="J48" s="3"/>
+      <c r="J48" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A49" s="3" t="s">
@@ -2430,19 +2430,109 @@
         <v>0</v>
       </c>
       <c r="C49" s="3">
-        <v>211042</v>
+        <v>211038</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="3"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3">
+        <v>211039</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3">
+        <v>10</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A51" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3">
+        <v>211040</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3">
+        <v>3</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A52" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3">
+        <v>211041</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3">
+        <v>3</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3">
+        <v>211042</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <v>3</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipLegendConfig.xlsx
+++ b/Excel/EquipLegendConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -235,13 +235,34 @@
     <t>7E+7</t>
   </si>
   <si>
-    <t>最高承伤10%</t>
-  </si>
-  <si>
     <t>寻宝项链</t>
   </si>
   <si>
     <t>寻宝玉带</t>
+  </si>
+  <si>
+    <t>背刺之刺</t>
+  </si>
+  <si>
+    <t>8E+7</t>
+  </si>
+  <si>
+    <t>背刺面罩</t>
+  </si>
+  <si>
+    <t>背刺之镯</t>
+  </si>
+  <si>
+    <t>斩杀板甲</t>
+  </si>
+  <si>
+    <t>1E+8</t>
+  </si>
+  <si>
+    <t>斩杀扳指</t>
+  </si>
+  <si>
+    <t>斩杀铁履</t>
   </si>
   <si>
     <t>幸运项链</t>
@@ -2158,9 +2179,7 @@
       <c r="I33" s="2">
         <v>45</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A34" s="3"/>
@@ -2169,7 +2188,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E34" s="3">
         <v>81</v>
@@ -2195,7 +2214,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3">
         <v>82</v>
@@ -2213,53 +2232,155 @@
         <v>45</v>
       </c>
       <c r="J35" s="3"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:10">
+      <c r="C36" s="3">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F36" s="3">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1">
+        <v>11</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I36" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:10">
+      <c r="C37" s="3">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F37" s="3">
+        <v>15</v>
+      </c>
+      <c r="G37" s="1">
+        <v>11</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I37" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="38" customFormat="1" customHeight="1" spans="1:10">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
+      <c r="C38" s="3">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F38" s="3">
+        <v>15</v>
+      </c>
+      <c r="G38" s="1">
+        <v>11</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I38" s="2">
+        <v>50</v>
+      </c>
       <c r="J38" s="1"/>
     </row>
     <row r="39" customFormat="1" customHeight="1" spans="1:10">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="C39" s="3">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F39" s="3">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1">
+        <v>12</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I39" s="2">
+        <v>55</v>
+      </c>
       <c r="J39" s="1"/>
     </row>
     <row r="40" customFormat="1" customHeight="1" spans="1:10">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
+      <c r="C40" s="3">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F40" s="3">
+        <v>20</v>
+      </c>
+      <c r="G40" s="1">
+        <v>12</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" s="2">
+        <v>55</v>
+      </c>
       <c r="J40" s="1"/>
     </row>
     <row r="41" customFormat="1" customHeight="1" spans="1:10">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="C41" s="3">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1003</v>
+      </c>
+      <c r="F41" s="3">
+        <v>20</v>
+      </c>
+      <c r="G41" s="1">
+        <v>12</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="2">
+        <v>55</v>
+      </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" customFormat="1" customHeight="1" spans="1:10">
@@ -2273,7 +2394,7 @@
         <v>211031</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -2283,7 +2404,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2297,7 +2418,7 @@
         <v>211032</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -2319,7 +2440,7 @@
         <v>211033</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -2341,7 +2462,7 @@
         <v>211034</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -2351,7 +2472,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2365,7 +2486,7 @@
         <v>211035</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
@@ -2387,7 +2508,7 @@
         <v>211036</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -2409,7 +2530,7 @@
         <v>211037</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -2419,7 +2540,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
       <c r="J48" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2433,7 +2554,7 @@
         <v>211038</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -2455,7 +2576,7 @@
         <v>211039</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -2477,7 +2598,7 @@
         <v>211040</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -2487,7 +2608,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
       <c r="J51" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -2501,7 +2622,7 @@
         <v>211041</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -2523,7 +2644,7 @@
         <v>211042</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
